--- a/econ-research_test.xlsx
+++ b/econ-research_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emelindo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AD79D87-F205-4D69-955E-000BBD8F27ED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472242BF-70FD-4391-BCDF-677E72FBF344}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{96972AFD-256D-41B3-BB7C-D6FB6464D72D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{96972AFD-256D-41B3-BB7C-D6FB6464D72D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
